--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\MinHyeong2DProject\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\Fantastic4\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C332237-FC6A-4B45-B271-23902C802810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3056752-D81F-4810-B797-F29EBDE10DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,17 +25,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
   <si>
     <t>캐릭터 고유 ID</t>
-  </si>
-  <si>
-    <t>enemy_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>enemy_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>MaxHp</t>
@@ -54,10 +46,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>방어력</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>(name)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -70,48 +58,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>종점 도달 시 깎이는 체력</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Defense</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>enum</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동 방식</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ground</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>enemy_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sky</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>enemy_04</t>
-  </si>
-  <si>
-    <t>enemy_05</t>
-  </si>
-  <si>
-    <t>MoveType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>PenaltyLife</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>RewardGold</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -153,6 +99,30 @@
   </si>
   <si>
     <t>Prefab/Enemy/enemy_05</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy_02</t>
+  </si>
+  <si>
+    <t>Enemy_03</t>
+  </si>
+  <si>
+    <t>Enemy_04</t>
+  </si>
+  <si>
+    <t>Enemy_05</t>
+  </si>
+  <si>
+    <t>특수능력 ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AbilityId</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -160,7 +130,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -222,13 +192,6 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color theme="7" tint="-0.249977111117893"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -274,7 +237,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -297,26 +260,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -336,7 +284,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -350,7 +297,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -360,13 +306,10 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -587,289 +530,227 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:O1000"/>
+  <dimension ref="A1:M1000"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" style="2" customWidth="1"/>
     <col min="3" max="3" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.28515625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" style="2" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="25.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.5703125" style="2"/>
+    <col min="6" max="6" width="25.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="12.5703125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" customHeight="1">
+    <row r="1" spans="1:13" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>10</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+    </row>
+    <row r="2" spans="1:13" ht="12.75">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+    </row>
+    <row r="3" spans="1:13" s="14" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A3" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+    </row>
+    <row r="4" spans="1:13" s="16" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A4" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="19">
+        <v>50</v>
+      </c>
+      <c r="C4" s="19">
+        <v>2.5</v>
+      </c>
+      <c r="D4" s="19"/>
+      <c r="E4" s="20">
+        <v>50</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-    </row>
-    <row r="2" spans="1:15" ht="12.75">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-    </row>
-    <row r="3" spans="1:15" s="15" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="13" t="s">
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+    </row>
+    <row r="5" spans="1:13" s="16" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A5" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="18">
+        <v>100</v>
+      </c>
+      <c r="C5" s="18">
+        <v>2</v>
+      </c>
+      <c r="D5" s="18"/>
+      <c r="E5" s="20">
+        <v>75</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+    </row>
+    <row r="6" spans="1:13" s="16" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A6" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="20">
+        <v>75</v>
+      </c>
+      <c r="C6" s="18">
+        <v>2.5</v>
+      </c>
+      <c r="D6" s="18"/>
+      <c r="E6" s="20">
+        <v>75</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+    </row>
+    <row r="7" spans="1:13" s="16" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A7" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="20">
+        <v>75</v>
+      </c>
+      <c r="C7" s="19">
         <v>3</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="D7" s="19"/>
+      <c r="E7" s="20">
+        <v>75</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+    </row>
+    <row r="8" spans="1:13" s="16" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A8" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-    </row>
-    <row r="4" spans="1:15" s="17" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A4" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="21">
-        <v>50</v>
-      </c>
-      <c r="C4" s="21">
-        <v>2.5</v>
-      </c>
-      <c r="D4" s="22">
-        <v>2</v>
-      </c>
-      <c r="E4" s="22">
-        <v>50</v>
-      </c>
-      <c r="F4" s="23">
-        <v>1</v>
-      </c>
-      <c r="G4" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
-    </row>
-    <row r="5" spans="1:15" s="17" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A5" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="20">
-        <v>100</v>
-      </c>
-      <c r="C5" s="20">
-        <v>2</v>
-      </c>
-      <c r="D5" s="22">
-        <v>5</v>
-      </c>
-      <c r="E5" s="22">
-        <v>75</v>
-      </c>
-      <c r="F5" s="22">
-        <v>1</v>
-      </c>
-      <c r="G5" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
-    </row>
-    <row r="6" spans="1:15" s="17" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A6" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="22">
-        <v>75</v>
-      </c>
-      <c r="C6" s="20">
-        <v>2.5</v>
-      </c>
-      <c r="D6" s="22">
-        <v>6</v>
-      </c>
-      <c r="E6" s="22">
-        <v>75</v>
-      </c>
-      <c r="F6" s="22">
-        <v>1</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-    </row>
-    <row r="7" spans="1:15" s="17" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A7" s="19" t="s">
+      <c r="B8" s="18">
+        <v>300</v>
+      </c>
+      <c r="C8" s="21">
+        <v>1.5</v>
+      </c>
+      <c r="D8" s="21"/>
+      <c r="E8" s="20">
+        <v>150</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="22">
-        <v>75</v>
-      </c>
-      <c r="C7" s="21">
-        <v>3</v>
-      </c>
-      <c r="D7" s="22">
-        <v>6</v>
-      </c>
-      <c r="E7" s="22">
-        <v>75</v>
-      </c>
-      <c r="F7" s="24">
-        <v>1</v>
-      </c>
-      <c r="G7" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="16"/>
-      <c r="O7" s="16"/>
-    </row>
-    <row r="8" spans="1:15" s="17" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A8" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="20">
-        <v>300</v>
-      </c>
-      <c r="C8" s="25">
-        <v>1.5</v>
-      </c>
-      <c r="D8" s="22">
-        <v>8</v>
-      </c>
-      <c r="E8" s="22">
-        <v>150</v>
-      </c>
-      <c r="F8" s="22">
-        <v>2</v>
-      </c>
-      <c r="G8" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-    </row>
-    <row r="9" spans="1:15" s="17" customFormat="1" ht="15.75" customHeight="1">
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+    </row>
+    <row r="9" spans="1:13" s="16" customFormat="1" ht="15.75" customHeight="1">
       <c r="B9" s="3"/>
       <c r="C9" s="5"/>
-      <c r="D9" s="1"/>
+      <c r="D9" s="5"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
-    </row>
-    <row r="10" spans="1:15" s="17" customFormat="1" ht="15.75" customHeight="1">
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+    </row>
+    <row r="10" spans="1:13" s="16" customFormat="1" ht="15.75" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -879,14 +760,12 @@
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
-    </row>
-    <row r="11" spans="1:15" s="17" customFormat="1" ht="15.75" customHeight="1">
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+    </row>
+    <row r="11" spans="1:13" s="16" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -896,48 +775,42 @@
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="16"/>
-    </row>
-    <row r="12" spans="1:15" s="17" customFormat="1" ht="15.75" customHeight="1">
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+    </row>
+    <row r="12" spans="1:13" s="16" customFormat="1" ht="15.75" customHeight="1">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
-      <c r="D12" s="1"/>
+      <c r="D12" s="5"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="16"/>
-    </row>
-    <row r="13" spans="1:15" s="17" customFormat="1" ht="15.75" customHeight="1">
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+    </row>
+    <row r="13" spans="1:13" s="16" customFormat="1" ht="15.75" customHeight="1">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
-      <c r="D13" s="1"/>
+      <c r="D13" s="3"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16"/>
-    </row>
-    <row r="14" spans="1:15" s="17" customFormat="1" ht="15.75" customHeight="1">
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+    </row>
+    <row r="14" spans="1:13" s="16" customFormat="1" ht="15.75" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -947,14 +820,12 @@
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="16"/>
-    </row>
-    <row r="15" spans="1:15" s="17" customFormat="1" ht="15.75" customHeight="1">
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+    </row>
+    <row r="15" spans="1:13" s="16" customFormat="1" ht="15.75" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -964,262 +835,229 @@
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="16"/>
-    </row>
-    <row r="16" spans="1:15" s="17" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="1"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+    </row>
+    <row r="16" spans="1:13" s="16" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="17" spans="1:11" s="17" customFormat="1" ht="15.75" customHeight="1">
+    </row>
+    <row r="17" spans="1:9" s="16" customFormat="1" ht="15.75" customHeight="1">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
+      <c r="D17" s="4"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-    </row>
-    <row r="18" spans="1:11" s="17" customFormat="1" ht="15.75" customHeight="1">
+    </row>
+    <row r="18" spans="1:9" s="16" customFormat="1" ht="15.75" customHeight="1">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
-      <c r="D18" s="1"/>
+      <c r="D18" s="4"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-    </row>
-    <row r="19" spans="1:11" s="17" customFormat="1" ht="15.75" customHeight="1">
+    </row>
+    <row r="19" spans="1:9" s="16" customFormat="1" ht="15.75" customHeight="1">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
-      <c r="D19" s="1"/>
+      <c r="D19" s="4"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-    </row>
-    <row r="20" spans="1:11" s="17" customFormat="1" ht="15.75" customHeight="1">
+    </row>
+    <row r="20" spans="1:9" s="16" customFormat="1" ht="15.75" customHeight="1">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
-      <c r="D20" s="1"/>
+      <c r="D20" s="4"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-    </row>
-    <row r="21" spans="1:11" ht="15.75" customHeight="1">
+    </row>
+    <row r="21" spans="1:9" ht="15.75" customHeight="1">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="7"/>
+      <c r="D21" s="8"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-    </row>
-    <row r="22" spans="1:11" ht="15.75" customHeight="1">
+    </row>
+    <row r="22" spans="1:9" ht="15.75" customHeight="1">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-    </row>
-    <row r="23" spans="1:11" ht="15.75" customHeight="1">
+    </row>
+    <row r="23" spans="1:9" ht="15.75" customHeight="1">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="7"/>
+      <c r="D23" s="8"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-    </row>
-    <row r="24" spans="1:11" ht="15.75" customHeight="1">
+    </row>
+    <row r="24" spans="1:9" ht="15.75" customHeight="1">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
-      <c r="D24" s="7"/>
+      <c r="D24" s="8"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-    </row>
-    <row r="25" spans="1:11" ht="15.75" customHeight="1">
+    </row>
+    <row r="25" spans="1:9" ht="15.75" customHeight="1">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
-      <c r="D25" s="7"/>
+      <c r="D25" s="8"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-    </row>
-    <row r="26" spans="1:11" ht="15.75" customHeight="1">
+    </row>
+    <row r="26" spans="1:9" ht="15.75" customHeight="1">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
-      <c r="D26" s="7"/>
+      <c r="D26" s="9"/>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-    </row>
-    <row r="27" spans="1:11" ht="15.75" customHeight="1">
+    </row>
+    <row r="27" spans="1:9" ht="15.75" customHeight="1">
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
-      <c r="D27" s="7"/>
+      <c r="D27" s="9"/>
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-    </row>
-    <row r="28" spans="1:11" ht="15.75" customHeight="1">
+    </row>
+    <row r="28" spans="1:9" ht="15.75" customHeight="1">
       <c r="A28" s="9"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
-      <c r="D28" s="7"/>
+      <c r="D28" s="9"/>
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-    </row>
-    <row r="29" spans="1:11" ht="15.75" customHeight="1">
+    </row>
+    <row r="29" spans="1:9" ht="15.75" customHeight="1">
       <c r="A29" s="9"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
-      <c r="D29" s="7"/>
+      <c r="D29" s="9"/>
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-    </row>
-    <row r="30" spans="1:11" ht="15.75" customHeight="1">
+    </row>
+    <row r="30" spans="1:9" ht="15.75" customHeight="1">
       <c r="A30" s="9"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
-      <c r="D30" s="7"/>
+      <c r="D30" s="9"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-    </row>
-    <row r="31" spans="1:11" ht="15.75" customHeight="1">
+    </row>
+    <row r="31" spans="1:9" ht="15.75" customHeight="1">
       <c r="A31" s="9"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
-      <c r="D31" s="7"/>
+      <c r="D31" s="9"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="G31" s="7"/>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-    </row>
-    <row r="32" spans="1:11" ht="15.75" customHeight="1">
+    </row>
+    <row r="32" spans="1:9" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="10"/>
       <c r="C32" s="10"/>
-      <c r="D32" s="7"/>
+      <c r="D32" s="10"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-    </row>
-    <row r="33" spans="1:3" ht="15.75" customHeight="1">
+    </row>
+    <row r="33" spans="1:4" ht="15.75" customHeight="1">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
-    </row>
-    <row r="34" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D33" s="6"/>
+    </row>
+    <row r="34" spans="1:4" ht="15.75" customHeight="1">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
-    </row>
-    <row r="35" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D34" s="6"/>
+    </row>
+    <row r="35" spans="1:4" ht="15.75" customHeight="1">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
-    </row>
-    <row r="36" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="37" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:3" ht="15.75" customHeight="1"/>
+      <c r="D35" s="6"/>
+    </row>
+    <row r="36" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="37" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\Fantastic4\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3056752-D81F-4810-B797-F29EBDE10DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB87BC0E-F1A8-4183-8479-7BF2773B84CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -82,26 +82,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Prefab/Enemy/enemy_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefab/Enemy/enemy_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefab/Enemy/enemy_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefab/Enemy/enemy_04</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefab/Enemy/enemy_05</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Enemy_01</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -123,6 +103,26 @@
   </si>
   <si>
     <t>AbilityId</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefab/Enemy/Enemy_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefab/Enemy/Enemy_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefab/Enemy/Enemy_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefab/Enemy/Enemy_04</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefab/Enemy/Enemy_05</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -553,7 +553,7 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>7</v>
@@ -599,7 +599,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>8</v>
@@ -613,7 +613,7 @@
     </row>
     <row r="4" spans="1:13" s="16" customFormat="1" ht="15.75" customHeight="1">
       <c r="A4" s="18" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B4" s="19">
         <v>50</v>
@@ -626,7 +626,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -638,7 +638,7 @@
     </row>
     <row r="5" spans="1:13" s="16" customFormat="1" ht="15.75" customHeight="1">
       <c r="A5" s="18" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B5" s="18">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>75</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -663,7 +663,7 @@
     </row>
     <row r="6" spans="1:13" s="16" customFormat="1" ht="15.75" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B6" s="20">
         <v>75</v>
@@ -676,7 +676,7 @@
         <v>75</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -688,7 +688,7 @@
     </row>
     <row r="7" spans="1:13" s="16" customFormat="1" ht="15.75" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B7" s="20">
         <v>75</v>
@@ -701,7 +701,7 @@
         <v>75</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -713,7 +713,7 @@
     </row>
     <row r="8" spans="1:13" s="16" customFormat="1" ht="15.75" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B8" s="18">
         <v>300</v>
@@ -726,7 +726,7 @@
         <v>150</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\Fantastic4\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB87BC0E-F1A8-4183-8479-7BF2773B84CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{243E80B2-9591-4F87-BFD7-D7977B583349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -82,22 +82,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Enemy_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enemy_02</t>
-  </si>
-  <si>
-    <t>Enemy_03</t>
-  </si>
-  <si>
-    <t>Enemy_04</t>
-  </si>
-  <si>
-    <t>Enemy_05</t>
-  </si>
-  <si>
     <t>특수능력 ID</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -106,23 +90,43 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Prefab/Enemy/Enemy_01</t>
+    <t>Enemy_Normal</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy_Cup</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy_Crazgy</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy_Doctor</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy_Special</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefab/Enemy/Enemy_Normal</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Prefab/Enemy/Enemy_02</t>
+    <t>Prefab/Enemy/Enemy_Cup</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Prefab/Enemy/Enemy_03</t>
+    <t>Prefab/Enemy/Enemy_Crazy</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Prefab/Enemy/Enemy_04</t>
+    <t>Prefab/Enemy/Enemy_Doctor</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Prefab/Enemy/Enemy_05</t>
+    <t>Prefab/Enemy/Enemy_Special</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -130,7 +134,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -192,8 +196,14 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -236,8 +246,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -260,11 +276,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border diagonalUp="1" diagonalDown="1">
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -312,6 +343,10 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -538,7 +573,7 @@
     <col min="3" max="3" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.5703125" style="2" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="12.5703125" style="2"/>
   </cols>
   <sheetData>
@@ -553,7 +588,7 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>7</v>
@@ -599,7 +634,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>8</v>
@@ -612,8 +647,8 @@
       <c r="I3" s="13"/>
     </row>
     <row r="4" spans="1:13" s="16" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A4" s="18" t="s">
-        <v>14</v>
+      <c r="A4" s="23" t="s">
+        <v>16</v>
       </c>
       <c r="B4" s="19">
         <v>50</v>
@@ -637,11 +672,11 @@
       <c r="M4" s="15"/>
     </row>
     <row r="5" spans="1:13" s="16" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A5" s="18" t="s">
-        <v>15</v>
+      <c r="A5" s="23" t="s">
+        <v>17</v>
       </c>
       <c r="B5" s="18">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="C5" s="18">
         <v>2</v>
@@ -662,14 +697,14 @@
       <c r="M5" s="15"/>
     </row>
     <row r="6" spans="1:13" s="16" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A6" s="18" t="s">
-        <v>16</v>
+      <c r="A6" s="24" t="s">
+        <v>18</v>
       </c>
       <c r="B6" s="20">
         <v>75</v>
       </c>
       <c r="C6" s="18">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="D6" s="18"/>
       <c r="E6" s="20">
@@ -687,8 +722,8 @@
       <c r="M6" s="15"/>
     </row>
     <row r="7" spans="1:13" s="16" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A7" s="18" t="s">
-        <v>17</v>
+      <c r="A7" s="24" t="s">
+        <v>19</v>
       </c>
       <c r="B7" s="20">
         <v>75</v>
@@ -712,14 +747,14 @@
       <c r="M7" s="15"/>
     </row>
     <row r="8" spans="1:13" s="16" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A8" s="18" t="s">
-        <v>18</v>
+      <c r="A8" s="24" t="s">
+        <v>20</v>
       </c>
       <c r="B8" s="18">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="C8" s="21">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="D8" s="21"/>
       <c r="E8" s="20">

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\Fantastic4\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{243E80B2-9591-4F87-BFD7-D7977B583349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B6645E-934C-4171-BADD-948C930346A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -127,6 +127,10 @@
   </si>
   <si>
     <t>Prefab/Enemy/Enemy_Special</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ability_04</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -731,7 +735,9 @@
       <c r="C7" s="19">
         <v>3</v>
       </c>
-      <c r="D7" s="19"/>
+      <c r="D7" s="19" t="s">
+        <v>26</v>
+      </c>
       <c r="E7" s="20">
         <v>75</v>
       </c>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\Fantastic4\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GameProjects\Fantastic4\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB87BC0E-F1A8-4183-8479-7BF2773B84CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{843E7519-FB17-45D9-A6E6-900EA7C5BD86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,9 @@
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="zgynNiv2YVTupuAxVwKvj3LXvSi69gCaqo2XUeu/LZo="/>
     </ext>
@@ -669,7 +672,7 @@
         <v>75</v>
       </c>
       <c r="C6" s="18">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="D6" s="18"/>
       <c r="E6" s="20">

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -1,22 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\Fantastic4\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GameProjects\Fantastic4\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B6645E-934C-4171-BADD-948C930346A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CF3E940-B674-4D14-AE01-B29541A76A07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11025" yWindow="735" windowWidth="16470" windowHeight="14115" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="zgynNiv2YVTupuAxVwKvj3LXvSi69gCaqo2XUeu/LZo="/>
     </ext>
@@ -98,10 +101,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>Enemy_Crazgy</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>Enemy_Doctor</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -132,6 +131,10 @@
   <si>
     <t>Ability_04</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy_Crazy</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -665,7 +668,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -690,7 +693,7 @@
         <v>75</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -702,7 +705,7 @@
     </row>
     <row r="6" spans="1:13" s="16" customFormat="1" ht="15.75" customHeight="1">
       <c r="A6" s="24" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B6" s="20">
         <v>75</v>
@@ -715,7 +718,7 @@
         <v>75</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -727,7 +730,7 @@
     </row>
     <row r="7" spans="1:13" s="16" customFormat="1" ht="15.75" customHeight="1">
       <c r="A7" s="24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" s="20">
         <v>75</v>
@@ -736,13 +739,13 @@
         <v>3</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E7" s="20">
         <v>75</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -754,7 +757,7 @@
     </row>
     <row r="8" spans="1:13" s="16" customFormat="1" ht="15.75" customHeight="1">
       <c r="A8" s="24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" s="18">
         <v>200</v>
@@ -767,7 +770,7 @@
         <v>150</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
